--- a/output_boron/boron_Intermediate_guillermic_2022.xlsx
+++ b/output_boron/boron_Intermediate_guillermic_2022.xlsx
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">10.5194/cp-18-183-2022</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/boron_isotopes_guillermic_2022.xlsx</t>
+    <t xml:space="preserve">boron_isotopes_guillermic_2022_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">MC-ICP-MS</t>
   </si>
   <si>
-    <t xml:space="preserve">Scenario 1A- G17/Caves2016</t>
+    <t xml:space="preserve">Scenario 1A- G17/Caves2016; Scenario 2A- L02/Caves2016; Scenario 3A- RH13/Caves2016</t>
   </si>
   <si>
     <t xml:space="preserve">ODP 806_B_3_4_86_88</t>
@@ -1672,7 +1672,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1732,12 +1732,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1851,7 +1845,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1933,7 +1927,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2540,7 +2533,7 @@
       <c r="B5" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" t="s">
         <v>242</v>
       </c>
       <c r="D5" t="s">
@@ -2617,7 +2610,7 @@
       <c r="B6" t="s">
         <v>241</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" t="s">
         <v>242</v>
       </c>
       <c r="D6" t="s">
@@ -2694,7 +2687,7 @@
       <c r="B7" t="s">
         <v>241</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" t="s">
         <v>242</v>
       </c>
       <c r="D7" t="s">
@@ -2771,7 +2764,7 @@
       <c r="B8" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" t="s">
         <v>242</v>
       </c>
       <c r="D8" t="s">
@@ -2848,7 +2841,7 @@
       <c r="B9" t="s">
         <v>241</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" t="s">
         <v>242</v>
       </c>
       <c r="D9" t="s">
@@ -2925,7 +2918,7 @@
       <c r="B10" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" t="s">
         <v>242</v>
       </c>
       <c r="D10" t="s">
@@ -3002,7 +2995,7 @@
       <c r="B11" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" t="s">
         <v>242</v>
       </c>
       <c r="D11" t="s">
@@ -3079,7 +3072,7 @@
       <c r="B12" t="s">
         <v>241</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" t="s">
         <v>242</v>
       </c>
       <c r="D12" t="s">
@@ -3156,7 +3149,7 @@
       <c r="B13" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" t="s">
         <v>242</v>
       </c>
       <c r="D13" t="s">
@@ -3233,7 +3226,7 @@
       <c r="B14" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" t="s">
         <v>242</v>
       </c>
       <c r="D14" t="s">
@@ -3310,7 +3303,7 @@
       <c r="B15" t="s">
         <v>241</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" t="s">
         <v>242</v>
       </c>
       <c r="D15" t="s">
@@ -3387,7 +3380,7 @@
       <c r="B16" t="s">
         <v>241</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" t="s">
         <v>242</v>
       </c>
       <c r="D16" t="s">
@@ -3464,7 +3457,7 @@
       <c r="B17" t="s">
         <v>241</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" t="s">
         <v>242</v>
       </c>
       <c r="D17" t="s">
@@ -3541,7 +3534,7 @@
       <c r="B18" t="s">
         <v>241</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" t="s">
         <v>242</v>
       </c>
       <c r="D18" t="s">
@@ -3618,7 +3611,7 @@
       <c r="B19" t="s">
         <v>241</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" t="s">
         <v>242</v>
       </c>
       <c r="D19" t="s">
@@ -3695,7 +3688,7 @@
       <c r="B20" t="s">
         <v>241</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" t="s">
         <v>242</v>
       </c>
       <c r="D20" t="s">
@@ -3772,7 +3765,7 @@
       <c r="B21" t="s">
         <v>241</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" t="s">
         <v>242</v>
       </c>
       <c r="D21" t="s">
@@ -3849,7 +3842,7 @@
       <c r="B22" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" t="s">
         <v>242</v>
       </c>
       <c r="D22" t="s">
@@ -3926,7 +3919,7 @@
       <c r="B23" t="s">
         <v>241</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" t="s">
         <v>242</v>
       </c>
       <c r="D23" t="s">
@@ -4003,7 +3996,7 @@
       <c r="B24" t="s">
         <v>241</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" t="s">
         <v>242</v>
       </c>
       <c r="D24" t="s">
@@ -4080,7 +4073,7 @@
       <c r="B25" t="s">
         <v>241</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" t="s">
         <v>242</v>
       </c>
       <c r="D25" t="s">
@@ -4157,7 +4150,7 @@
       <c r="B26" t="s">
         <v>241</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" t="s">
         <v>242</v>
       </c>
       <c r="D26" t="s">
@@ -4234,7 +4227,7 @@
       <c r="B27" t="s">
         <v>241</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" t="s">
         <v>242</v>
       </c>
       <c r="D27" t="s">
@@ -4311,7 +4304,7 @@
       <c r="B28" t="s">
         <v>241</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" t="s">
         <v>242</v>
       </c>
       <c r="D28" t="s">
@@ -4388,7 +4381,7 @@
       <c r="B29" t="s">
         <v>241</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" t="s">
         <v>242</v>
       </c>
       <c r="D29" t="s">
@@ -4465,7 +4458,7 @@
       <c r="B30" t="s">
         <v>241</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" t="s">
         <v>242</v>
       </c>
       <c r="D30" t="s">
@@ -4542,7 +4535,7 @@
       <c r="B31" t="s">
         <v>241</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" t="s">
         <v>242</v>
       </c>
       <c r="D31" t="s">
@@ -4619,7 +4612,7 @@
       <c r="B32" t="s">
         <v>241</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" t="s">
         <v>242</v>
       </c>
       <c r="D32" t="s">
@@ -4696,7 +4689,7 @@
       <c r="B33" t="s">
         <v>241</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" t="s">
         <v>242</v>
       </c>
       <c r="D33" t="s">
@@ -4773,7 +4766,7 @@
       <c r="B34" t="s">
         <v>241</v>
       </c>
-      <c r="C34" s="29" t="s">
+      <c r="C34" t="s">
         <v>242</v>
       </c>
       <c r="D34" t="s">
@@ -4850,7 +4843,7 @@
       <c r="B35" t="s">
         <v>241</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" t="s">
         <v>242</v>
       </c>
       <c r="D35" t="s">
@@ -4927,7 +4920,7 @@
       <c r="B36" t="s">
         <v>241</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="C36" t="s">
         <v>242</v>
       </c>
       <c r="D36" t="s">
@@ -5004,7 +4997,7 @@
       <c r="B37" t="s">
         <v>241</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" t="s">
         <v>242</v>
       </c>
       <c r="D37" t="s">
@@ -5081,7 +5074,7 @@
       <c r="B38" t="s">
         <v>241</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="C38" t="s">
         <v>242</v>
       </c>
       <c r="D38" t="s">
@@ -5158,7 +5151,7 @@
       <c r="B39" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" t="s">
         <v>242</v>
       </c>
       <c r="D39" t="s">
@@ -5235,7 +5228,7 @@
       <c r="B40" t="s">
         <v>241</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="C40" t="s">
         <v>242</v>
       </c>
       <c r="D40" t="s">
@@ -5312,7 +5305,7 @@
       <c r="B41" t="s">
         <v>241</v>
       </c>
-      <c r="C41" s="29" t="s">
+      <c r="C41" t="s">
         <v>242</v>
       </c>
       <c r="D41" t="s">
@@ -5389,7 +5382,7 @@
       <c r="B42" t="s">
         <v>241</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C42" t="s">
         <v>242</v>
       </c>
       <c r="D42" t="s">
@@ -5466,7 +5459,7 @@
       <c r="B43" t="s">
         <v>241</v>
       </c>
-      <c r="C43" s="29" t="s">
+      <c r="C43" t="s">
         <v>242</v>
       </c>
       <c r="D43" t="s">
@@ -5543,7 +5536,7 @@
       <c r="B44" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="C44" t="s">
         <v>242</v>
       </c>
       <c r="D44" t="s">
@@ -5620,7 +5613,7 @@
       <c r="B45" t="s">
         <v>241</v>
       </c>
-      <c r="C45" s="29" t="s">
+      <c r="C45" t="s">
         <v>242</v>
       </c>
       <c r="D45" t="s">
@@ -5697,7 +5690,7 @@
       <c r="B46" t="s">
         <v>241</v>
       </c>
-      <c r="C46" s="29" t="s">
+      <c r="C46" t="s">
         <v>242</v>
       </c>
       <c r="D46" t="s">
@@ -5774,7 +5767,7 @@
       <c r="B47" t="s">
         <v>241</v>
       </c>
-      <c r="C47" s="29" t="s">
+      <c r="C47" t="s">
         <v>242</v>
       </c>
       <c r="D47" t="s">
@@ -5851,7 +5844,7 @@
       <c r="B48" t="s">
         <v>241</v>
       </c>
-      <c r="C48" s="29" t="s">
+      <c r="C48" t="s">
         <v>242</v>
       </c>
       <c r="D48" t="s">
@@ -5928,7 +5921,7 @@
       <c r="B49" t="s">
         <v>241</v>
       </c>
-      <c r="C49" s="29" t="s">
+      <c r="C49" t="s">
         <v>242</v>
       </c>
       <c r="D49" t="s">
@@ -6005,7 +5998,7 @@
       <c r="B50" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="29" t="s">
+      <c r="C50" t="s">
         <v>242</v>
       </c>
       <c r="D50" t="s">
@@ -6082,7 +6075,7 @@
       <c r="B51" t="s">
         <v>241</v>
       </c>
-      <c r="C51" s="29" t="s">
+      <c r="C51" t="s">
         <v>242</v>
       </c>
       <c r="D51" t="s">
@@ -6159,7 +6152,7 @@
       <c r="B52" t="s">
         <v>241</v>
       </c>
-      <c r="C52" s="29" t="s">
+      <c r="C52" t="s">
         <v>242</v>
       </c>
       <c r="D52" t="s">
@@ -6236,7 +6229,7 @@
       <c r="B53" t="s">
         <v>241</v>
       </c>
-      <c r="C53" s="29" t="s">
+      <c r="C53" t="s">
         <v>242</v>
       </c>
       <c r="D53" t="s">
@@ -6313,7 +6306,7 @@
       <c r="B54" t="s">
         <v>241</v>
       </c>
-      <c r="C54" s="29" t="s">
+      <c r="C54" t="s">
         <v>242</v>
       </c>
       <c r="D54" t="s">
@@ -6390,7 +6383,7 @@
       <c r="B55" t="s">
         <v>241</v>
       </c>
-      <c r="C55" s="29" t="s">
+      <c r="C55" t="s">
         <v>242</v>
       </c>
       <c r="D55" t="s">
@@ -6467,7 +6460,7 @@
       <c r="B56" t="s">
         <v>241</v>
       </c>
-      <c r="C56" s="29" t="s">
+      <c r="C56" t="s">
         <v>242</v>
       </c>
       <c r="D56" t="s">
@@ -6544,7 +6537,7 @@
       <c r="B57" t="s">
         <v>241</v>
       </c>
-      <c r="C57" s="29" t="s">
+      <c r="C57" t="s">
         <v>242</v>
       </c>
       <c r="D57" t="s">
@@ -6621,7 +6614,7 @@
       <c r="B58" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="29" t="s">
+      <c r="C58" t="s">
         <v>242</v>
       </c>
       <c r="D58" t="s">
@@ -6698,7 +6691,7 @@
       <c r="B59" t="s">
         <v>241</v>
       </c>
-      <c r="C59" s="29" t="s">
+      <c r="C59" t="s">
         <v>242</v>
       </c>
       <c r="D59" t="s">
@@ -6775,7 +6768,7 @@
       <c r="B60" t="s">
         <v>241</v>
       </c>
-      <c r="C60" s="29" t="s">
+      <c r="C60" t="s">
         <v>242</v>
       </c>
       <c r="D60" t="s">
@@ -6852,7 +6845,7 @@
       <c r="B61" t="s">
         <v>241</v>
       </c>
-      <c r="C61" s="29" t="s">
+      <c r="C61" t="s">
         <v>242</v>
       </c>
       <c r="D61" t="s">
@@ -6929,7 +6922,7 @@
       <c r="B62" t="s">
         <v>241</v>
       </c>
-      <c r="C62" s="29" t="s">
+      <c r="C62" t="s">
         <v>242</v>
       </c>
       <c r="D62" t="s">
@@ -7006,7 +6999,7 @@
       <c r="B63" t="s">
         <v>241</v>
       </c>
-      <c r="C63" s="29" t="s">
+      <c r="C63" t="s">
         <v>242</v>
       </c>
       <c r="D63" t="s">
@@ -7083,7 +7076,7 @@
       <c r="B64" t="s">
         <v>241</v>
       </c>
-      <c r="C64" s="29" t="s">
+      <c r="C64" t="s">
         <v>242</v>
       </c>
       <c r="D64" t="s">
@@ -7160,7 +7153,7 @@
       <c r="B65" t="s">
         <v>241</v>
       </c>
-      <c r="C65" s="29" t="s">
+      <c r="C65" t="s">
         <v>242</v>
       </c>
       <c r="D65" t="s">
@@ -7237,7 +7230,7 @@
       <c r="B66" t="s">
         <v>241</v>
       </c>
-      <c r="C66" s="29" t="s">
+      <c r="C66" t="s">
         <v>242</v>
       </c>
       <c r="D66" t="s">
@@ -7314,7 +7307,7 @@
       <c r="B67" t="s">
         <v>241</v>
       </c>
-      <c r="C67" s="29" t="s">
+      <c r="C67" t="s">
         <v>242</v>
       </c>
       <c r="D67" t="s">
@@ -7391,7 +7384,7 @@
       <c r="B68" t="s">
         <v>241</v>
       </c>
-      <c r="C68" s="29" t="s">
+      <c r="C68" t="s">
         <v>242</v>
       </c>
       <c r="D68" t="s">
@@ -7468,7 +7461,7 @@
       <c r="B69" t="s">
         <v>241</v>
       </c>
-      <c r="C69" s="29" t="s">
+      <c r="C69" t="s">
         <v>242</v>
       </c>
       <c r="D69" t="s">
@@ -7545,7 +7538,7 @@
       <c r="B70" t="s">
         <v>241</v>
       </c>
-      <c r="C70" s="29" t="s">
+      <c r="C70" t="s">
         <v>242</v>
       </c>
       <c r="D70" t="s">
@@ -7622,7 +7615,7 @@
       <c r="B71" t="s">
         <v>241</v>
       </c>
-      <c r="C71" s="29" t="s">
+      <c r="C71" t="s">
         <v>242</v>
       </c>
       <c r="D71" t="s">
@@ -7699,7 +7692,7 @@
       <c r="B72" t="s">
         <v>241</v>
       </c>
-      <c r="C72" s="29" t="s">
+      <c r="C72" t="s">
         <v>242</v>
       </c>
       <c r="D72" t="s">
@@ -7776,7 +7769,7 @@
       <c r="B73" t="s">
         <v>241</v>
       </c>
-      <c r="C73" s="29" t="s">
+      <c r="C73" t="s">
         <v>242</v>
       </c>
       <c r="D73" t="s">
@@ -7853,7 +7846,7 @@
       <c r="B74" t="s">
         <v>241</v>
       </c>
-      <c r="C74" s="29" t="s">
+      <c r="C74" t="s">
         <v>242</v>
       </c>
       <c r="D74" t="s">
@@ -7930,7 +7923,7 @@
       <c r="B75" t="s">
         <v>241</v>
       </c>
-      <c r="C75" s="29" t="s">
+      <c r="C75" t="s">
         <v>242</v>
       </c>
       <c r="D75" t="s">
@@ -8007,7 +8000,7 @@
       <c r="B76" t="s">
         <v>241</v>
       </c>
-      <c r="C76" s="29" t="s">
+      <c r="C76" t="s">
         <v>242</v>
       </c>
       <c r="D76" t="s">
@@ -8084,7 +8077,7 @@
       <c r="B77" t="s">
         <v>241</v>
       </c>
-      <c r="C77" s="29" t="s">
+      <c r="C77" t="s">
         <v>242</v>
       </c>
       <c r="D77" t="s">
@@ -8161,7 +8154,7 @@
       <c r="B78" t="s">
         <v>241</v>
       </c>
-      <c r="C78" s="29" t="s">
+      <c r="C78" t="s">
         <v>242</v>
       </c>
       <c r="D78" t="s">
@@ -8238,7 +8231,7 @@
       <c r="B79" t="s">
         <v>241</v>
       </c>
-      <c r="C79" s="29" t="s">
+      <c r="C79" t="s">
         <v>242</v>
       </c>
       <c r="D79" t="s">
@@ -8315,7 +8308,7 @@
       <c r="B80" t="s">
         <v>241</v>
       </c>
-      <c r="C80" s="29" t="s">
+      <c r="C80" t="s">
         <v>242</v>
       </c>
       <c r="D80" t="s">
@@ -8392,7 +8385,7 @@
       <c r="B81" t="s">
         <v>241</v>
       </c>
-      <c r="C81" s="29" t="s">
+      <c r="C81" t="s">
         <v>242</v>
       </c>
       <c r="D81" t="s">
@@ -8469,7 +8462,7 @@
       <c r="B82" t="s">
         <v>241</v>
       </c>
-      <c r="C82" s="29" t="s">
+      <c r="C82" t="s">
         <v>242</v>
       </c>
       <c r="D82" t="s">
@@ -8546,7 +8539,7 @@
       <c r="B83" t="s">
         <v>241</v>
       </c>
-      <c r="C83" s="29" t="s">
+      <c r="C83" t="s">
         <v>242</v>
       </c>
       <c r="D83" t="s">
@@ -8623,7 +8616,7 @@
       <c r="B84" t="s">
         <v>241</v>
       </c>
-      <c r="C84" s="29" t="s">
+      <c r="C84" t="s">
         <v>242</v>
       </c>
       <c r="D84" t="s">
@@ -8700,7 +8693,7 @@
       <c r="B85" t="s">
         <v>241</v>
       </c>
-      <c r="C85" s="29" t="s">
+      <c r="C85" t="s">
         <v>242</v>
       </c>
       <c r="D85" t="s">
@@ -8777,7 +8770,7 @@
       <c r="B86" t="s">
         <v>241</v>
       </c>
-      <c r="C86" s="29" t="s">
+      <c r="C86" t="s">
         <v>242</v>
       </c>
       <c r="D86" t="s">
@@ -8854,7 +8847,7 @@
       <c r="B87" t="s">
         <v>241</v>
       </c>
-      <c r="C87" s="29" t="s">
+      <c r="C87" t="s">
         <v>242</v>
       </c>
       <c r="D87" t="s">
@@ -8931,7 +8924,7 @@
       <c r="B88" t="s">
         <v>241</v>
       </c>
-      <c r="C88" s="29" t="s">
+      <c r="C88" t="s">
         <v>242</v>
       </c>
       <c r="D88" t="s">
@@ -9008,7 +9001,7 @@
       <c r="B89" t="s">
         <v>241</v>
       </c>
-      <c r="C89" s="29" t="s">
+      <c r="C89" t="s">
         <v>242</v>
       </c>
       <c r="D89" t="s">
@@ -9085,7 +9078,7 @@
       <c r="B90" t="s">
         <v>241</v>
       </c>
-      <c r="C90" s="29" t="s">
+      <c r="C90" t="s">
         <v>242</v>
       </c>
       <c r="D90" t="s">
@@ -9162,7 +9155,7 @@
       <c r="B91" t="s">
         <v>241</v>
       </c>
-      <c r="C91" s="29" t="s">
+      <c r="C91" t="s">
         <v>242</v>
       </c>
       <c r="D91" t="s">
@@ -9239,7 +9232,7 @@
       <c r="B92" t="s">
         <v>241</v>
       </c>
-      <c r="C92" s="29" t="s">
+      <c r="C92" t="s">
         <v>242</v>
       </c>
       <c r="D92" t="s">
@@ -9316,7 +9309,7 @@
       <c r="B93" t="s">
         <v>241</v>
       </c>
-      <c r="C93" s="29" t="s">
+      <c r="C93" t="s">
         <v>242</v>
       </c>
       <c r="D93" t="s">
@@ -9431,97 +9424,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-    <hyperlink ref="C33" r:id="rId29h"/>
-    <hyperlink ref="C34" r:id="rId30h"/>
-    <hyperlink ref="C35" r:id="rId31h"/>
-    <hyperlink ref="C36" r:id="rId32h"/>
-    <hyperlink ref="C37" r:id="rId33h"/>
-    <hyperlink ref="C38" r:id="rId34h"/>
-    <hyperlink ref="C39" r:id="rId35h"/>
-    <hyperlink ref="C40" r:id="rId36h"/>
-    <hyperlink ref="C41" r:id="rId37h"/>
-    <hyperlink ref="C42" r:id="rId38h"/>
-    <hyperlink ref="C43" r:id="rId39h"/>
-    <hyperlink ref="C44" r:id="rId40h"/>
-    <hyperlink ref="C45" r:id="rId41h"/>
-    <hyperlink ref="C46" r:id="rId42h"/>
-    <hyperlink ref="C47" r:id="rId43h"/>
-    <hyperlink ref="C48" r:id="rId44h"/>
-    <hyperlink ref="C49" r:id="rId45h"/>
-    <hyperlink ref="C50" r:id="rId46h"/>
-    <hyperlink ref="C51" r:id="rId47h"/>
-    <hyperlink ref="C52" r:id="rId48h"/>
-    <hyperlink ref="C53" r:id="rId49h"/>
-    <hyperlink ref="C54" r:id="rId50h"/>
-    <hyperlink ref="C55" r:id="rId51h"/>
-    <hyperlink ref="C56" r:id="rId52h"/>
-    <hyperlink ref="C57" r:id="rId53h"/>
-    <hyperlink ref="C58" r:id="rId54h"/>
-    <hyperlink ref="C59" r:id="rId55h"/>
-    <hyperlink ref="C60" r:id="rId56h"/>
-    <hyperlink ref="C61" r:id="rId57h"/>
-    <hyperlink ref="C62" r:id="rId58h"/>
-    <hyperlink ref="C63" r:id="rId59h"/>
-    <hyperlink ref="C64" r:id="rId60h"/>
-    <hyperlink ref="C65" r:id="rId61h"/>
-    <hyperlink ref="C66" r:id="rId62h"/>
-    <hyperlink ref="C67" r:id="rId63h"/>
-    <hyperlink ref="C68" r:id="rId64h"/>
-    <hyperlink ref="C69" r:id="rId65h"/>
-    <hyperlink ref="C70" r:id="rId66h"/>
-    <hyperlink ref="C71" r:id="rId67h"/>
-    <hyperlink ref="C72" r:id="rId68h"/>
-    <hyperlink ref="C73" r:id="rId69h"/>
-    <hyperlink ref="C74" r:id="rId70h"/>
-    <hyperlink ref="C75" r:id="rId71h"/>
-    <hyperlink ref="C76" r:id="rId72h"/>
-    <hyperlink ref="C77" r:id="rId73h"/>
-    <hyperlink ref="C78" r:id="rId74h"/>
-    <hyperlink ref="C79" r:id="rId75h"/>
-    <hyperlink ref="C80" r:id="rId76h"/>
-    <hyperlink ref="C81" r:id="rId77h"/>
-    <hyperlink ref="C82" r:id="rId78h"/>
-    <hyperlink ref="C83" r:id="rId79h"/>
-    <hyperlink ref="C84" r:id="rId80h"/>
-    <hyperlink ref="C85" r:id="rId81h"/>
-    <hyperlink ref="C86" r:id="rId82h"/>
-    <hyperlink ref="C87" r:id="rId83h"/>
-    <hyperlink ref="C88" r:id="rId84h"/>
-    <hyperlink ref="C89" r:id="rId85h"/>
-    <hyperlink ref="C90" r:id="rId86h"/>
-    <hyperlink ref="C91" r:id="rId87h"/>
-    <hyperlink ref="C92" r:id="rId88h"/>
-    <hyperlink ref="C93" r:id="rId89h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
